--- a/SGC-CKN/Excel/fab26366-c20e-47b1-ba53-19e557e9179d_Lô_CT-02_P1-76_D800_03-04-2026.xlsx
+++ b/SGC-CKN/Excel/fab26366-c20e-47b1-ba53-19e557e9179d_Lô_CT-02_P1-76_D800_03-04-2026.xlsx
@@ -1292,16 +1292,16 @@
         <v>-12</v>
       </c>
       <c r="G15" s="18">
-        <v>-20</v>
+        <v>-20.8</v>
       </c>
       <c r="H15" s="18">
         <v>0.63</v>
       </c>
       <c r="I15" s="18">
-        <v>8</v>
+        <v>8.8</v>
       </c>
       <c r="J15" s="8">
-        <v>12.63</v>
+        <v>13.89</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1324,7 +1324,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="21">
-        <v>-20</v>
+        <v>-20.8</v>
       </c>
       <c r="G16" s="21">
         <v>-26</v>
@@ -1333,10 +1333,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" s="21">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J16" s="8">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
@@ -1680,16 +1680,16 @@
         <v>-12</v>
       </c>
       <c r="F6" s="18">
-        <v>-20</v>
+        <v>-20.8</v>
       </c>
       <c r="G6" s="18">
         <v>0.63</v>
       </c>
       <c r="H6" s="18">
-        <v>8</v>
+        <v>8.8</v>
       </c>
       <c r="I6" s="8">
-        <v>12.63</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1706,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-20</v>
+        <v>-20.8</v>
       </c>
       <c r="F7" s="21">
         <v>-26</v>
@@ -1715,10 +1715,10 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="21">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I7" s="8">
-        <v>12</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
